--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_individual_h_11.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_individual_h_11.xlsx
@@ -658,7 +658,7 @@
         <v>0.05258738218505241</v>
       </c>
       <c r="C2" t="n">
-        <v>68340492</v>
+        <v>6212772</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>68340492</v>
+        <v>6212772</v>
       </c>
       <c r="K2" t="n">
-        <v>45565118</v>
+        <v>3599839</v>
       </c>
       <c r="L2" t="n">
-        <v>25278108</v>
+        <v>1729526</v>
       </c>
       <c r="M2" t="n">
-        <v>6188017</v>
+        <v>358806</v>
       </c>
       <c r="N2" t="n">
-        <v>321365</v>
+        <v>13015</v>
       </c>
       <c r="O2" t="n">
-        <v>3775384</v>
+        <v>230037</v>
       </c>
       <c r="P2" t="n">
-        <v>1563614</v>
+        <v>101382</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999070763587952</v>
+        <v>0.9998083114624023</v>
       </c>
       <c r="R2" t="n">
-        <v>0.844504714012146</v>
+        <v>0.7338399887084961</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7035641074180603</v>
+        <v>0.5293267965316772</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6143949627876282</v>
+        <v>0.392584353685379</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4300158023834229</v>
+        <v>0.1927291601896286</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6734588146209717</v>
+        <v>0.4515523016452789</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7378858327865601</v>
+        <v>0.5263234376907349</v>
       </c>
       <c r="X2" t="n">
-        <v>68340492</v>
+        <v>6212772</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>68340492</v>
+        <v>6212772</v>
       </c>
       <c r="AF2" t="n">
-        <v>44488870</v>
+        <v>3557004</v>
       </c>
       <c r="AG2" t="n">
-        <v>23473597</v>
+        <v>1648362</v>
       </c>
       <c r="AH2" t="n">
-        <v>5649662</v>
+        <v>337891</v>
       </c>
       <c r="AI2" t="n">
-        <v>298959</v>
+        <v>12661</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3480563</v>
+        <v>216237</v>
       </c>
       <c r="AK2" t="n">
-        <v>1471361</v>
+        <v>95469</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.8190881609916687</v>
+        <v>0.7203711271286011</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.6660129427909851</v>
+        <v>0.5144560933113098</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.5545850396156311</v>
+        <v>0.3648505210876465</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.3075209856033325</v>
+        <v>0.1432596296072006</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.6227976083755493</v>
+        <v>0.4256181418895721</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.6921143531799316</v>
+        <v>0.4939848780632019</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.01618567928948078</v>
       </c>
       <c r="C3" t="n">
-        <v>1968</v>
+        <v>444</v>
       </c>
       <c r="D3" t="n">
-        <v>45565118</v>
+        <v>3599839</v>
       </c>
       <c r="E3" t="n">
-        <v>7589489</v>
+        <v>1105414</v>
       </c>
       <c r="F3" t="n">
-        <v>424598</v>
+        <v>88417</v>
       </c>
       <c r="G3" t="n">
-        <v>51684</v>
+        <v>8231</v>
       </c>
       <c r="H3" t="n">
-        <v>39196</v>
+        <v>11929</v>
       </c>
       <c r="I3" t="n">
-        <v>6026</v>
+        <v>2118</v>
       </c>
       <c r="J3" t="n">
-        <v>108427556</v>
+        <v>9856437</v>
       </c>
       <c r="K3" t="n">
-        <v>114706597</v>
+        <v>9948365</v>
       </c>
       <c r="L3" t="n">
-        <v>130353762</v>
+        <v>11228109</v>
       </c>
       <c r="M3" t="n">
-        <v>162621789</v>
+        <v>14573961</v>
       </c>
       <c r="N3" t="n">
-        <v>175370266</v>
+        <v>15926392</v>
       </c>
       <c r="O3" t="n">
-        <v>169333705</v>
+        <v>15278886</v>
       </c>
       <c r="P3" t="n">
-        <v>174090423</v>
+        <v>15785227</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8488589525222778</v>
+        <v>0.7474140524864197</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7066826820373535</v>
+        <v>0.5233993530273438</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6025976538658142</v>
+        <v>0.3811870217323303</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3285382986068726</v>
+        <v>0.1454303711652756</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6729598045349121</v>
+        <v>0.4491901099681854</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7345928549766541</v>
+        <v>0.522770881652832</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>44488870</v>
+        <v>3557004</v>
       </c>
       <c r="Z3" t="n">
-        <v>8374549</v>
+        <v>1114075</v>
       </c>
       <c r="AA3" t="n">
-        <v>582424</v>
+        <v>106809</v>
       </c>
       <c r="AB3" t="n">
-        <v>169979</v>
+        <v>20519</v>
       </c>
       <c r="AC3" t="n">
-        <v>53096</v>
+        <v>14993</v>
       </c>
       <c r="AD3" t="n">
-        <v>9161</v>
+        <v>2992</v>
       </c>
       <c r="AE3" t="n">
-        <v>108433908</v>
+        <v>9857628</v>
       </c>
       <c r="AF3" t="n">
-        <v>113270073</v>
+        <v>9873274</v>
       </c>
       <c r="AG3" t="n">
-        <v>129232943</v>
+        <v>11210265</v>
       </c>
       <c r="AH3" t="n">
-        <v>161967971</v>
+        <v>14540897</v>
       </c>
       <c r="AI3" t="n">
-        <v>175123035</v>
+        <v>15905190</v>
       </c>
       <c r="AJ3" t="n">
-        <v>169056251</v>
+        <v>15266468</v>
       </c>
       <c r="AK3" t="n">
-        <v>173991323</v>
+        <v>15778674</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.8288089036941528</v>
+        <v>0.7385204434394836</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.6562352180480957</v>
+        <v>0.4988369941711426</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.5501719117164612</v>
+        <v>0.3589674234390259</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.3056321740150452</v>
+        <v>0.1414747536182404</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.6204081773757935</v>
+        <v>0.422243058681488</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.6912519931793213</v>
+        <v>0.4922808110713959</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.1032982568032969</v>
       </c>
       <c r="C4" t="n">
-        <v>754</v>
+        <v>163</v>
       </c>
       <c r="D4" t="n">
-        <v>7771945</v>
+        <v>1173545</v>
       </c>
       <c r="E4" t="n">
-        <v>25278108</v>
+        <v>1729526</v>
       </c>
       <c r="F4" t="n">
-        <v>2229776</v>
+        <v>302098</v>
       </c>
       <c r="G4" t="n">
-        <v>92815</v>
+        <v>15035</v>
       </c>
       <c r="H4" t="n">
-        <v>345715</v>
+        <v>71328</v>
       </c>
       <c r="I4" t="n">
-        <v>50984</v>
+        <v>12715</v>
       </c>
       <c r="J4" t="n">
-        <v>6352</v>
+        <v>1191</v>
       </c>
       <c r="K4" t="n">
-        <v>8389724</v>
+        <v>1305643</v>
       </c>
       <c r="L4" t="n">
-        <v>10650541</v>
+        <v>1537881</v>
       </c>
       <c r="M4" t="n">
-        <v>3883708</v>
+        <v>555153</v>
       </c>
       <c r="N4" t="n">
-        <v>425968</v>
+        <v>54515</v>
       </c>
       <c r="O4" t="n">
-        <v>1830577</v>
+        <v>279399</v>
       </c>
       <c r="P4" t="n">
-        <v>555432</v>
+        <v>91241</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.99995356798172</v>
+        <v>0.9999041557312012</v>
       </c>
       <c r="R4" t="n">
-        <v>0.846676230430603</v>
+        <v>0.74056476354599</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7051199078559875</v>
+        <v>0.5263463854789734</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6084391474723816</v>
+        <v>0.3868017196655273</v>
       </c>
       <c r="U4" t="n">
-        <v>0.372489333152771</v>
+        <v>0.1657718867063522</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6732091903686523</v>
+        <v>0.4503681063652039</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7362356781959534</v>
+        <v>0.5245411396026611</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>9045309</v>
+        <v>1226903</v>
       </c>
       <c r="Z4" t="n">
-        <v>23473597</v>
+        <v>1648362</v>
       </c>
       <c r="AA4" t="n">
-        <v>2587276</v>
+        <v>313588</v>
       </c>
       <c r="AB4" t="n">
-        <v>175500</v>
+        <v>22550</v>
       </c>
       <c r="AC4" t="n">
-        <v>422135</v>
+        <v>78235</v>
       </c>
       <c r="AD4" t="n">
-        <v>66280</v>
+        <v>14772</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>9826248</v>
+        <v>1380734</v>
       </c>
       <c r="AG4" t="n">
-        <v>11771360</v>
+        <v>1555725</v>
       </c>
       <c r="AH4" t="n">
-        <v>4537526</v>
+        <v>588217</v>
       </c>
       <c r="AI4" t="n">
-        <v>673199</v>
+        <v>75717</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2108031</v>
+        <v>291817</v>
       </c>
       <c r="AK4" t="n">
-        <v>654532</v>
+        <v>97794</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.8239198923110962</v>
+        <v>0.7293328642845154</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.6610879302024841</v>
+        <v>0.5065262317657471</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.5523696541786194</v>
+        <v>0.3618850708007812</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.3065736591815948</v>
+        <v>0.1423616111278534</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.6216005682945251</v>
+        <v>0.4239239096641541</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.6916828751564026</v>
+        <v>0.4931313991546631</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1209</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
-        <v>438612</v>
+        <v>97802</v>
       </c>
       <c r="E5" t="n">
-        <v>2457275</v>
+        <v>318413</v>
       </c>
       <c r="F5" t="n">
-        <v>6188017</v>
+        <v>358806</v>
       </c>
       <c r="G5" t="n">
-        <v>153979</v>
+        <v>17113</v>
       </c>
       <c r="H5" t="n">
-        <v>903199</v>
+        <v>124031</v>
       </c>
       <c r="I5" t="n">
-        <v>126612</v>
+        <v>24896</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>8112961</v>
+        <v>1216553</v>
       </c>
       <c r="L5" t="n">
-        <v>10491989</v>
+        <v>1574884</v>
       </c>
       <c r="M5" t="n">
-        <v>4080886</v>
+        <v>582480</v>
       </c>
       <c r="N5" t="n">
-        <v>656801</v>
+        <v>76478</v>
       </c>
       <c r="O5" t="n">
-        <v>1834734</v>
+        <v>282078</v>
       </c>
       <c r="P5" t="n">
-        <v>564931</v>
+        <v>92550</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999640583992004</v>
+        <v>0.9999259114265442</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9066454768180847</v>
+        <v>0.8430533409118652</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8803982138633728</v>
+        <v>0.8063044548034668</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9549448490142822</v>
+        <v>0.9292094111442566</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9938748478889465</v>
+        <v>0.9918488264083862</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9792656302452087</v>
+        <v>0.9650614261627197</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9936621785163879</v>
+        <v>0.9885633587837219</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>557886</v>
+        <v>113275</v>
       </c>
       <c r="Z5" t="n">
-        <v>2696336</v>
+        <v>318124</v>
       </c>
       <c r="AA5" t="n">
-        <v>5649662</v>
+        <v>337891</v>
       </c>
       <c r="AB5" t="n">
-        <v>183791</v>
+        <v>18281</v>
       </c>
       <c r="AC5" t="n">
-        <v>1027269</v>
+        <v>126497</v>
       </c>
       <c r="AD5" t="n">
-        <v>153959</v>
+        <v>27218</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>9189209</v>
+        <v>1259388</v>
       </c>
       <c r="AG5" t="n">
-        <v>12296500</v>
+        <v>1656048</v>
       </c>
       <c r="AH5" t="n">
-        <v>4619241</v>
+        <v>603395</v>
       </c>
       <c r="AI5" t="n">
-        <v>679207</v>
+        <v>76832</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2129555</v>
+        <v>295878</v>
       </c>
       <c r="AK5" t="n">
-        <v>657184</v>
+        <v>98463</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.8924309611320496</v>
+        <v>0.8357152342796326</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.8638498783111572</v>
+        <v>0.8001435399055481</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9482008218765259</v>
+        <v>0.925850510597229</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9923495650291443</v>
+        <v>0.9905074834823608</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9760282635688782</v>
+        <v>0.9634299874305725</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9925796985626221</v>
+        <v>0.987787663936615</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1644</v>
+        <v>232</v>
       </c>
       <c r="D6" t="n">
-        <v>133203</v>
+        <v>18233</v>
       </c>
       <c r="E6" t="n">
-        <v>185685</v>
+        <v>24077</v>
       </c>
       <c r="F6" t="n">
-        <v>199059</v>
+        <v>17806</v>
       </c>
       <c r="G6" t="n">
-        <v>321365</v>
+        <v>13015</v>
       </c>
       <c r="H6" t="n">
-        <v>116399</v>
+        <v>12966</v>
       </c>
       <c r="I6" t="n">
-        <v>20811</v>
+        <v>3164</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>155149</v>
+        <v>19464</v>
       </c>
       <c r="Z6" t="n">
-        <v>185421</v>
+        <v>23674</v>
       </c>
       <c r="AA6" t="n">
-        <v>188617</v>
+        <v>17518</v>
       </c>
       <c r="AB6" t="n">
-        <v>298959</v>
+        <v>12661</v>
       </c>
       <c r="AC6" t="n">
-        <v>126226</v>
+        <v>12841</v>
       </c>
       <c r="AD6" t="n">
-        <v>23794</v>
+        <v>3335</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>504</v>
+        <v>98</v>
       </c>
       <c r="D7" t="n">
-        <v>43378</v>
+        <v>14816</v>
       </c>
       <c r="E7" t="n">
-        <v>379306</v>
+        <v>79749</v>
       </c>
       <c r="F7" t="n">
-        <v>949147</v>
+        <v>127915</v>
       </c>
       <c r="G7" t="n">
-        <v>111400</v>
+        <v>11152</v>
       </c>
       <c r="H7" t="n">
-        <v>3775384</v>
+        <v>230037</v>
       </c>
       <c r="I7" t="n">
-        <v>350999</v>
+        <v>48348</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>63239</v>
+        <v>19084</v>
       </c>
       <c r="Z7" t="n">
-        <v>464812</v>
+        <v>87959</v>
       </c>
       <c r="AA7" t="n">
-        <v>1076157</v>
+        <v>128273</v>
       </c>
       <c r="AB7" t="n">
-        <v>124009</v>
+        <v>11085</v>
       </c>
       <c r="AC7" t="n">
-        <v>3480563</v>
+        <v>216237</v>
       </c>
       <c r="AD7" t="n">
-        <v>401338</v>
+        <v>49477</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>273</v>
+        <v>29</v>
       </c>
       <c r="D8" t="n">
-        <v>2586</v>
+        <v>1247</v>
       </c>
       <c r="E8" t="n">
-        <v>38786</v>
+        <v>10228</v>
       </c>
       <c r="F8" t="n">
-        <v>81128</v>
+        <v>18917</v>
       </c>
       <c r="G8" t="n">
-        <v>16090</v>
+        <v>2984</v>
       </c>
       <c r="H8" t="n">
-        <v>426068</v>
+        <v>59145</v>
       </c>
       <c r="I8" t="n">
-        <v>1563614</v>
+        <v>101382</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>4665</v>
+        <v>2008</v>
       </c>
       <c r="Z8" t="n">
-        <v>50242</v>
+        <v>11893</v>
       </c>
       <c r="AA8" t="n">
-        <v>103052</v>
+        <v>22029</v>
       </c>
       <c r="AB8" t="n">
-        <v>19920</v>
+        <v>3282</v>
       </c>
       <c r="AC8" t="n">
-        <v>479305</v>
+        <v>59251</v>
       </c>
       <c r="AD8" t="n">
-        <v>1471361</v>
+        <v>95469</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
